--- a/jogos_2024-12-03.xlsx
+++ b/jogos_2024-12-03.xlsx
@@ -643,25 +643,25 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Dewa United</t>
+          <t>Arema</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>PSS Sleman</t>
+          <t>Persita</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" t="n">
         <v>1</v>
       </c>
-      <c r="I2" t="n">
-        <v>2</v>
-      </c>
       <c r="J2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -669,83 +669,83 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>1.69</v>
+        <v>1.65</v>
       </c>
       <c r="M2" t="n">
-        <v>3.65</v>
+        <v>3.48</v>
       </c>
       <c r="N2" t="n">
-        <v>4.32</v>
+        <v>4.88</v>
       </c>
       <c r="O2" t="n">
-        <v>2.11</v>
+        <v>2.33</v>
       </c>
       <c r="P2" t="n">
-        <v>2.24</v>
+        <v>2.03</v>
       </c>
       <c r="Q2" t="n">
         <v>5</v>
       </c>
       <c r="R2" t="n">
-        <v>1.32</v>
+        <v>1.47</v>
       </c>
       <c r="S2" t="n">
-        <v>3.21</v>
+        <v>2.5</v>
       </c>
       <c r="T2" t="n">
-        <v>2.55</v>
+        <v>3.18</v>
       </c>
       <c r="U2" t="n">
-        <v>1.46</v>
+        <v>1.33</v>
       </c>
       <c r="V2" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="W2" t="n">
-        <v>1.24</v>
+        <v>1.36</v>
       </c>
       <c r="X2" t="n">
-        <v>3.7</v>
+        <v>2.9</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.64</v>
+        <v>1.98</v>
       </c>
       <c r="Z2" t="n">
-        <v>2.11</v>
+        <v>1.73</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.85</v>
+        <v>3.75</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.38</v>
+        <v>1.23</v>
       </c>
       <c r="AC2" t="n">
-        <v>1.79</v>
+        <v>2.04</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.92</v>
+        <v>1.69</v>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>['20', '45']</t>
+          <t>['45+4', '51', '90+6']</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>['25']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG2" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.93</v>
+        <v>1.83</v>
       </c>
       <c r="AI2" t="n">
-        <v>1.52</v>
+        <v>1.55</v>
       </c>
       <c r="AJ2" t="n">
-        <v>2.64</v>
+        <v>2.9</v>
       </c>
       <c r="AK2" s="3" t="n">
         <v>45629.22916666666</v>
@@ -772,109 +772,109 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Arema</t>
+          <t>Dewa United</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Persita</t>
+          <t>PSS Sleman</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I3" t="n">
+        <v>2</v>
+      </c>
+      <c r="J3" t="n">
         <v>1</v>
       </c>
-      <c r="J3" t="n">
-        <v>0</v>
-      </c>
       <c r="K3" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.65</v>
+        <v>1.69</v>
       </c>
       <c r="M3" t="n">
-        <v>3.48</v>
+        <v>3.65</v>
       </c>
       <c r="N3" t="n">
-        <v>4.88</v>
+        <v>4.32</v>
       </c>
       <c r="O3" t="n">
-        <v>2.33</v>
+        <v>2.11</v>
       </c>
       <c r="P3" t="n">
-        <v>2.03</v>
+        <v>2.24</v>
       </c>
       <c r="Q3" t="n">
         <v>5</v>
       </c>
       <c r="R3" t="n">
-        <v>1.47</v>
+        <v>1.32</v>
       </c>
       <c r="S3" t="n">
-        <v>2.5</v>
+        <v>3.21</v>
       </c>
       <c r="T3" t="n">
-        <v>3.18</v>
+        <v>2.55</v>
       </c>
       <c r="U3" t="n">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="V3" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="W3" t="n">
-        <v>1.36</v>
+        <v>1.24</v>
       </c>
       <c r="X3" t="n">
-        <v>2.9</v>
+        <v>3.7</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.98</v>
+        <v>1.64</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.73</v>
+        <v>2.11</v>
       </c>
       <c r="AA3" t="n">
-        <v>3.75</v>
+        <v>2.85</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.23</v>
+        <v>1.38</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.04</v>
+        <v>1.79</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.69</v>
+        <v>1.92</v>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>['45+4', '51', '90+6']</t>
+          <t>['20', '45']</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['25']</t>
         </is>
       </c>
       <c r="AG3" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.83</v>
+        <v>1.93</v>
       </c>
       <c r="AI3" t="n">
-        <v>1.55</v>
+        <v>1.52</v>
       </c>
       <c r="AJ3" t="n">
-        <v>2.9</v>
+        <v>2.64</v>
       </c>
       <c r="AK3" s="3" t="n">
         <v>45629.22916666666</v>
@@ -1030,16 +1030,16 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Voska Sport</t>
+          <t>Vardar</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Tikveš</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H5" t="n">
         <v>1</v>
@@ -1048,7 +1048,7 @@
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -1056,83 +1056,83 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="M5" t="n">
+        <v>3</v>
+      </c>
+      <c r="N5" t="n">
         <v>3.6</v>
       </c>
-      <c r="N5" t="n">
+      <c r="O5" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="P5" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="S5" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="T5" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="V5" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="W5" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="X5" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Z5" t="n">
         <v>1.5</v>
       </c>
-      <c r="O5" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="P5" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="Q5" t="n">
+      <c r="AA5" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AC5" t="n">
         <v>2.1</v>
       </c>
-      <c r="R5" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="S5" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="T5" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="U5" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="V5" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="W5" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="X5" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Z5" t="n">
+      <c r="AD5" t="n">
         <v>1.65</v>
       </c>
-      <c r="AA5" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>1.57</v>
-      </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['64']</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>['51']</t>
+          <t>['41']</t>
         </is>
       </c>
       <c r="AG5" t="n">
-        <v>1.95</v>
+        <v>1.23</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.13</v>
+        <v>1.6</v>
       </c>
       <c r="AI5" t="n">
-        <v>4.33</v>
+        <v>1.73</v>
       </c>
       <c r="AJ5" t="n">
-        <v>1.36</v>
+        <v>2.75</v>
       </c>
       <c r="AK5" s="3" t="n">
         <v>45629.375</v>
@@ -1149,7 +1149,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1159,25 +1159,25 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Igman Konjic</t>
+          <t>KF Gostivari</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Sileks</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -1185,83 +1185,83 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>6.2</v>
+        <v>1.91</v>
       </c>
       <c r="M6" t="n">
-        <v>4.4</v>
+        <v>3.1</v>
       </c>
       <c r="N6" t="n">
-        <v>1.45</v>
+        <v>3.75</v>
       </c>
       <c r="O6" t="n">
-        <v>5.5</v>
+        <v>2.63</v>
       </c>
       <c r="P6" t="n">
-        <v>2.3</v>
+        <v>1.91</v>
       </c>
       <c r="Q6" t="n">
-        <v>2</v>
+        <v>4.75</v>
       </c>
       <c r="R6" t="n">
-        <v>1.33</v>
+        <v>1.58</v>
       </c>
       <c r="S6" t="n">
-        <v>3.25</v>
+        <v>2.27</v>
       </c>
       <c r="T6" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="V6" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="W6" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="X6" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="Y6" t="n">
         <v>2.5</v>
       </c>
-      <c r="U6" t="n">
+      <c r="Z6" t="n">
         <v>1.5</v>
       </c>
-      <c r="V6" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W6" t="n">
+      <c r="AA6" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG6" t="n">
         <v>1.22</v>
       </c>
-      <c r="X6" t="n">
-        <v>4</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AE6" t="inlineStr">
-        <is>
-          <t>['40']</t>
-        </is>
-      </c>
-      <c r="AF6" t="inlineStr">
-        <is>
-          <t>['21']</t>
-        </is>
-      </c>
-      <c r="AG6" t="n">
-        <v>2.16</v>
-      </c>
       <c r="AH6" t="n">
-        <v>1.11</v>
+        <v>1.61</v>
       </c>
       <c r="AI6" t="n">
-        <v>3.4</v>
+        <v>1.62</v>
       </c>
       <c r="AJ6" t="n">
-        <v>1.33</v>
+        <v>3</v>
       </c>
       <c r="AK6" s="3" t="n">
         <v>45629.375</v>
@@ -1288,25 +1288,25 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Akademija Pandev</t>
+          <t>Shkupi</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rabotnički</t>
+          <t>Struga</t>
         </is>
       </c>
       <c r="G7" t="n">
+        <v>3</v>
+      </c>
+      <c r="H7" t="n">
         <v>1</v>
       </c>
-      <c r="H7" t="n">
-        <v>3</v>
-      </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -1314,43 +1314,43 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>3.2</v>
+        <v>2.8</v>
       </c>
       <c r="M7" t="n">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="N7" t="n">
-        <v>2.15</v>
+        <v>2.45</v>
       </c>
       <c r="O7" t="n">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="P7" t="n">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="R7" t="n">
-        <v>1.55</v>
+        <v>1.62</v>
       </c>
       <c r="S7" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="T7" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="V7" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="W7" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="X7" t="n">
         <v>2.3</v>
-      </c>
-      <c r="T7" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="U7" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="V7" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="W7" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="X7" t="n">
-        <v>2.35</v>
       </c>
       <c r="Y7" t="n">
         <v>2.63</v>
@@ -1359,10 +1359,10 @@
         <v>1.44</v>
       </c>
       <c r="AA7" t="n">
-        <v>5.5</v>
+        <v>4.85</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="AC7" t="n">
         <v>2.1</v>
@@ -1372,25 +1372,25 @@
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>['74']</t>
+          <t>['17', '32', '75']</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>['17', '44', '68']</t>
+          <t>['90+1']</t>
         </is>
       </c>
       <c r="AG7" t="n">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AI7" t="n">
-        <v>2.6</v>
+        <v>2.38</v>
       </c>
       <c r="AJ7" t="n">
-        <v>1.8</v>
+        <v>1.95</v>
       </c>
       <c r="AK7" s="3" t="n">
         <v>45629.375</v>
@@ -1675,25 +1675,25 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Vardar</t>
+          <t>Akademija Pandev</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tikveš</t>
+          <t>Rabotnički</t>
         </is>
       </c>
       <c r="G10" t="n">
         <v>1</v>
       </c>
       <c r="H10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -1701,55 +1701,55 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2</v>
+        <v>3.2</v>
       </c>
       <c r="M10" t="n">
         <v>3</v>
       </c>
       <c r="N10" t="n">
-        <v>3.6</v>
+        <v>2.15</v>
       </c>
       <c r="O10" t="n">
-        <v>2.88</v>
+        <v>4</v>
       </c>
       <c r="P10" t="n">
         <v>1.91</v>
       </c>
       <c r="Q10" t="n">
-        <v>4.33</v>
+        <v>3.1</v>
       </c>
       <c r="R10" t="n">
-        <v>1.58</v>
+        <v>1.55</v>
       </c>
       <c r="S10" t="n">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="T10" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="U10" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="V10" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="W10" t="n">
-        <v>1.49</v>
+        <v>1.55</v>
       </c>
       <c r="X10" t="n">
-        <v>2.43</v>
+        <v>2.35</v>
       </c>
       <c r="Y10" t="n">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AA10" t="n">
-        <v>4.5</v>
+        <v>5.5</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.16</v>
+        <v>1.11</v>
       </c>
       <c r="AC10" t="n">
         <v>2.1</v>
@@ -1759,25 +1759,25 @@
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>['64']</t>
+          <t>['74']</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>['41']</t>
+          <t>['17', '44', '68']</t>
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>1.23</v>
+        <v>1.53</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.6</v>
+        <v>1.3</v>
       </c>
       <c r="AI10" t="n">
-        <v>1.73</v>
+        <v>2.6</v>
       </c>
       <c r="AJ10" t="n">
-        <v>2.75</v>
+        <v>1.8</v>
       </c>
       <c r="AK10" s="3" t="n">
         <v>45629.375</v>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,25 +1804,25 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>KF Gostivari</t>
+          <t>Igman Konjic</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Sileks</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -1830,83 +1830,83 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.91</v>
+        <v>6.2</v>
       </c>
       <c r="M11" t="n">
-        <v>3.1</v>
+        <v>4.4</v>
       </c>
       <c r="N11" t="n">
-        <v>3.75</v>
+        <v>1.45</v>
       </c>
       <c r="O11" t="n">
-        <v>2.63</v>
+        <v>5.5</v>
       </c>
       <c r="P11" t="n">
-        <v>1.91</v>
+        <v>2.3</v>
       </c>
       <c r="Q11" t="n">
-        <v>4.75</v>
+        <v>2</v>
       </c>
       <c r="R11" t="n">
-        <v>1.58</v>
+        <v>1.33</v>
       </c>
       <c r="S11" t="n">
-        <v>2.27</v>
+        <v>3.25</v>
       </c>
       <c r="T11" t="n">
-        <v>3.65</v>
+        <v>2.5</v>
       </c>
       <c r="U11" t="n">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="V11" t="n">
-        <v>1.09</v>
+        <v>1.03</v>
       </c>
       <c r="W11" t="n">
-        <v>1.49</v>
+        <v>1.22</v>
       </c>
       <c r="X11" t="n">
-        <v>2.46</v>
+        <v>4</v>
       </c>
       <c r="Y11" t="n">
-        <v>2.5</v>
+        <v>1.67</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.5</v>
+        <v>2.07</v>
       </c>
       <c r="AA11" t="n">
-        <v>4.5</v>
+        <v>2.7</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.17</v>
+        <v>1.43</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.1</v>
+        <v>1.83</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.65</v>
+        <v>1.83</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['40']</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['21']</t>
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>1.22</v>
+        <v>2.16</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.61</v>
+        <v>1.11</v>
       </c>
       <c r="AI11" t="n">
-        <v>1.62</v>
+        <v>3.4</v>
       </c>
       <c r="AJ11" t="n">
-        <v>3</v>
+        <v>1.33</v>
       </c>
       <c r="AK11" s="3" t="n">
         <v>45629.375</v>
@@ -1933,22 +1933,22 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Shkupi</t>
+          <t>Voska Sport</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Struga</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H12" t="n">
         <v>1</v>
       </c>
       <c r="I12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1959,83 +1959,83 @@
         </is>
       </c>
       <c r="L12" t="n">
+        <v>6</v>
+      </c>
+      <c r="M12" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="N12" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="O12" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="P12" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="S12" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="T12" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="X12" t="n">
         <v>2.8</v>
       </c>
-      <c r="M12" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="N12" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="O12" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="P12" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="R12" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="S12" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="T12" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="U12" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="V12" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="W12" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="X12" t="n">
-        <v>2.3</v>
-      </c>
       <c r="Y12" t="n">
-        <v>2.63</v>
+        <v>2.2</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.44</v>
+        <v>1.65</v>
       </c>
       <c r="AA12" t="n">
-        <v>4.85</v>
+        <v>3.9</v>
       </c>
       <c r="AB12" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AE12" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF12" t="inlineStr">
+        <is>
+          <t>['51']</t>
+        </is>
+      </c>
+      <c r="AG12" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AH12" t="n">
         <v>1.13</v>
       </c>
-      <c r="AC12" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AE12" t="inlineStr">
-        <is>
-          <t>['17', '32', '75']</t>
-        </is>
-      </c>
-      <c r="AF12" t="inlineStr">
-        <is>
-          <t>['90+1']</t>
-        </is>
-      </c>
-      <c r="AG12" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>1.33</v>
-      </c>
       <c r="AI12" t="n">
-        <v>2.38</v>
+        <v>4.33</v>
       </c>
       <c r="AJ12" t="n">
-        <v>1.95</v>
+        <v>1.36</v>
       </c>
       <c r="AK12" s="3" t="n">
         <v>45629.375</v>
@@ -2052,7 +2052,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,22 +2062,22 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Cherno More</t>
+          <t>Tractor Sazi</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>Chadormalu SC</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -2088,65 +2088,65 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.42</v>
+        <v>1.55</v>
       </c>
       <c r="M13" t="n">
-        <v>4.2</v>
+        <v>3.3</v>
       </c>
       <c r="N13" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="O13" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="P13" t="n">
-        <v>2.2</v>
+        <v>1.95</v>
       </c>
       <c r="Q13" t="n">
-        <v>8.5</v>
+        <v>7</v>
       </c>
       <c r="R13" t="n">
-        <v>1.44</v>
+        <v>1.55</v>
       </c>
       <c r="S13" t="n">
-        <v>2.63</v>
+        <v>2.33</v>
       </c>
       <c r="T13" t="n">
-        <v>3.4</v>
+        <v>3.62</v>
       </c>
       <c r="U13" t="n">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="V13" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W13" t="n">
-        <v>1.35</v>
+        <v>1.48</v>
       </c>
       <c r="X13" t="n">
-        <v>3.05</v>
+        <v>2.37</v>
       </c>
       <c r="Y13" t="n">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.65</v>
+        <v>1.5</v>
       </c>
       <c r="AA13" t="n">
-        <v>3.65</v>
+        <v>4.7</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.26</v>
+        <v>1.17</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.5</v>
+        <v>2.49</v>
       </c>
       <c r="AD13" t="n">
         <v>1.5</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>['29', '31', '87', '89']</t>
+          <t>['84']</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
@@ -2155,16 +2155,16 @@
         </is>
       </c>
       <c r="AG13" t="n">
-        <v>1.07</v>
+        <v>1.14</v>
       </c>
       <c r="AH13" t="n">
-        <v>2.44</v>
+        <v>1.84</v>
       </c>
       <c r="AI13" t="n">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="AJ13" t="n">
-        <v>5.5</v>
+        <v>4.33</v>
       </c>
       <c r="AK13" s="3" t="n">
         <v>45629.41666666666</v>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,22 +2191,22 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Tractor Sazi</t>
+          <t>Cherno More</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Chadormalu SC</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -2217,65 +2217,65 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="M14" t="n">
-        <v>3.3</v>
+        <v>4.2</v>
       </c>
       <c r="N14" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="O14" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="P14" t="n">
-        <v>1.95</v>
+        <v>2.2</v>
       </c>
       <c r="Q14" t="n">
-        <v>7</v>
+        <v>8.5</v>
       </c>
       <c r="R14" t="n">
-        <v>1.55</v>
+        <v>1.44</v>
       </c>
       <c r="S14" t="n">
-        <v>2.33</v>
+        <v>2.63</v>
       </c>
       <c r="T14" t="n">
-        <v>3.62</v>
+        <v>3.4</v>
       </c>
       <c r="U14" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="V14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="X14" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AB14" t="n">
         <v>1.26</v>
       </c>
-      <c r="V14" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W14" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="X14" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="Y14" t="n">
+      <c r="AC14" t="n">
         <v>2.5</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>2.49</v>
       </c>
       <c r="AD14" t="n">
         <v>1.5</v>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>['84']</t>
+          <t>['29', '31', '87', '89']</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
@@ -2284,16 +2284,16 @@
         </is>
       </c>
       <c r="AG14" t="n">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.84</v>
+        <v>2.44</v>
       </c>
       <c r="AI14" t="n">
-        <v>1.4</v>
+        <v>1.25</v>
       </c>
       <c r="AJ14" t="n">
-        <v>4.33</v>
+        <v>5.5</v>
       </c>
       <c r="AK14" s="3" t="n">
         <v>45629.41666666666</v>
@@ -2310,7 +2310,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Nigeria NPFL</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,25 +2320,25 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Enyimba</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Enugu Rangers</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -2346,83 +2346,83 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>5.99</v>
+        <v>1.2</v>
       </c>
       <c r="M15" t="n">
-        <v>4.25</v>
+        <v>4.75</v>
       </c>
       <c r="N15" t="n">
-        <v>1.47</v>
+        <v>13</v>
       </c>
       <c r="O15" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="P15" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>15</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="S15" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="T15" t="n">
+        <v>3.84</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="V15" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="X15" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>5.05</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AE15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG15" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AJ15" t="n">
         <v>6.5</v>
-      </c>
-      <c r="P15" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="R15" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S15" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="T15" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="U15" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="V15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W15" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="X15" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>2</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AE15" t="inlineStr">
-        <is>
-          <t>['18', '65']</t>
-        </is>
-      </c>
-      <c r="AF15" t="inlineStr">
-        <is>
-          <t>['35', '45', '57']</t>
-        </is>
-      </c>
-      <c r="AG15" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AI15" t="n">
-        <v>4</v>
-      </c>
-      <c r="AJ15" t="n">
-        <v>1.29</v>
       </c>
       <c r="AK15" s="3" t="n">
         <v>45629.5</v>
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Nigeria NPFL</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,25 +2449,25 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Enyimba</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Enugu Rangers</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
@@ -2475,83 +2475,83 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.2</v>
+        <v>5.99</v>
       </c>
       <c r="M16" t="n">
-        <v>4.75</v>
+        <v>4.25</v>
       </c>
       <c r="N16" t="n">
-        <v>13</v>
+        <v>1.47</v>
       </c>
       <c r="O16" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="P16" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S16" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="V16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="X16" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD16" t="n">
         <v>1.73</v>
       </c>
-      <c r="P16" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>15</v>
-      </c>
-      <c r="R16" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="S16" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="T16" t="n">
-        <v>3.84</v>
-      </c>
-      <c r="U16" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="V16" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="W16" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="X16" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>5.05</v>
-      </c>
-      <c r="AB16" t="n">
+      <c r="AE16" t="inlineStr">
+        <is>
+          <t>['18', '65']</t>
+        </is>
+      </c>
+      <c r="AF16" t="inlineStr">
+        <is>
+          <t>['35', '45', '57']</t>
+        </is>
+      </c>
+      <c r="AG16" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AH16" t="n">
         <v>1.09</v>
       </c>
-      <c r="AC16" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AE16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG16" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>2.36</v>
-      </c>
       <c r="AI16" t="n">
-        <v>1.22</v>
+        <v>4</v>
       </c>
       <c r="AJ16" t="n">
-        <v>6.5</v>
+        <v>1.29</v>
       </c>
       <c r="AK16" s="3" t="n">
         <v>45629.5</v>
@@ -2955,7 +2955,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2965,19 +2965,19 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>MTK</t>
+          <t>RCD Mallorca</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Paksi SE</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H20" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I20" t="n">
         <v>1</v>
@@ -2991,28 +2991,28 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.39</v>
+        <v>5.25</v>
       </c>
       <c r="M20" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="N20" t="n">
-        <v>2.59</v>
+        <v>1.7</v>
       </c>
       <c r="O20" t="n">
-        <v>2.88</v>
+        <v>5</v>
       </c>
       <c r="P20" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q20" t="n">
         <v>2.25</v>
       </c>
-      <c r="Q20" t="n">
-        <v>3.4</v>
-      </c>
       <c r="R20" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="S20" t="n">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="T20" t="n">
         <v>2.63</v>
@@ -3021,53 +3021,53 @@
         <v>1.44</v>
       </c>
       <c r="V20" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="W20" t="n">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="X20" t="n">
-        <v>4.1</v>
+        <v>3.8</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.65</v>
+        <v>1.8</v>
       </c>
       <c r="Z20" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.7</v>
+        <v>2.89</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="AD20" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE20" t="inlineStr">
+        <is>
+          <t>['43']</t>
+        </is>
+      </c>
+      <c r="AF20" t="inlineStr">
+        <is>
+          <t>['12', '56', '74', '79', '84']</t>
+        </is>
+      </c>
+      <c r="AG20" t="n">
         <v>2.25</v>
       </c>
-      <c r="AE20" t="inlineStr">
-        <is>
-          <t>['15', '68', '77']</t>
-        </is>
-      </c>
-      <c r="AF20" t="inlineStr">
-        <is>
-          <t>['17']</t>
-        </is>
-      </c>
-      <c r="AG20" t="n">
-        <v>1.34</v>
-      </c>
       <c r="AH20" t="n">
-        <v>1.48</v>
+        <v>1.18</v>
       </c>
       <c r="AI20" t="n">
-        <v>1.73</v>
+        <v>3</v>
       </c>
       <c r="AJ20" t="n">
-        <v>2.2</v>
+        <v>1.44</v>
       </c>
       <c r="AK20" s="3" t="n">
         <v>45629.625</v>
@@ -3084,7 +3084,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3094,22 +3094,22 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RCD Mallorca</t>
+          <t>Sparta Praha</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Karviná</t>
         </is>
       </c>
       <c r="G21" t="n">
+        <v>4</v>
+      </c>
+      <c r="H21" t="n">
         <v>1</v>
       </c>
-      <c r="H21" t="n">
-        <v>5</v>
-      </c>
       <c r="I21" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J21" t="n">
         <v>1</v>
@@ -3120,83 +3120,83 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>5.25</v>
+        <v>1.23</v>
       </c>
       <c r="M21" t="n">
-        <v>3.6</v>
+        <v>6.3</v>
       </c>
       <c r="N21" t="n">
-        <v>1.7</v>
+        <v>10.7</v>
       </c>
       <c r="O21" t="n">
-        <v>5</v>
+        <v>1.5</v>
       </c>
       <c r="P21" t="n">
-        <v>2.3</v>
+        <v>3.1</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.25</v>
+        <v>9</v>
       </c>
       <c r="R21" t="n">
-        <v>1.36</v>
+        <v>1.2</v>
       </c>
       <c r="S21" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T21" t="n">
-        <v>2.63</v>
+        <v>1.95</v>
       </c>
       <c r="U21" t="n">
-        <v>1.44</v>
+        <v>1.75</v>
       </c>
       <c r="V21" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W21" t="n">
-        <v>1.19</v>
+        <v>1.1</v>
       </c>
       <c r="X21" t="n">
-        <v>3.8</v>
+        <v>5.75</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.8</v>
+        <v>1.45</v>
       </c>
       <c r="Z21" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AC21" t="n">
         <v>2</v>
       </c>
-      <c r="AA21" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>1.75</v>
-      </c>
       <c r="AD21" t="n">
-        <v>2</v>
+        <v>1.73</v>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>['43']</t>
+          <t>['2', '39', '45', '88']</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>['12', '56', '74', '79', '84']</t>
+          <t>['36']</t>
         </is>
       </c>
       <c r="AG21" t="n">
-        <v>2.25</v>
+        <v>1.05</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.18</v>
+        <v>4.33</v>
       </c>
       <c r="AI21" t="n">
-        <v>3</v>
+        <v>1.17</v>
       </c>
       <c r="AJ21" t="n">
-        <v>1.44</v>
+        <v>4.7</v>
       </c>
       <c r="AK21" s="3" t="n">
         <v>45629.625</v>
@@ -3213,7 +3213,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3223,25 +3223,25 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Maccabi Netanya</t>
+          <t>MTK</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ashdod</t>
+          <t>Paksi SE</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
@@ -3249,83 +3249,83 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.9</v>
+        <v>2.39</v>
       </c>
       <c r="M22" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="N22" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="O22" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="P22" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Q22" t="n">
         <v>3.4</v>
       </c>
-      <c r="N22" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="O22" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="P22" t="n">
+      <c r="R22" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S22" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="V22" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W22" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="X22" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="Z22" t="n">
         <v>2.2</v>
       </c>
-      <c r="Q22" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="R22" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="S22" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="T22" t="n">
+      <c r="AA22" t="n">
         <v>2.7</v>
       </c>
-      <c r="U22" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="V22" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="W22" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="X22" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>3.1</v>
-      </c>
       <c r="AB22" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AE22" t="inlineStr">
+        <is>
+          <t>['15', '68', '77']</t>
+        </is>
+      </c>
+      <c r="AF22" t="inlineStr">
+        <is>
+          <t>['17']</t>
+        </is>
+      </c>
+      <c r="AG22" t="n">
         <v>1.34</v>
       </c>
-      <c r="AC22" t="n">
+      <c r="AH22" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AI22" t="n">
         <v>1.73</v>
       </c>
-      <c r="AD22" t="n">
-        <v>2</v>
-      </c>
-      <c r="AE22" t="inlineStr">
-        <is>
-          <t>['27', '44']</t>
-        </is>
-      </c>
-      <c r="AF22" t="inlineStr">
-        <is>
-          <t>['54', '54']</t>
-        </is>
-      </c>
-      <c r="AG22" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AH22" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AI22" t="n">
-        <v>1.57</v>
-      </c>
       <c r="AJ22" t="n">
-        <v>2.6</v>
+        <v>2.2</v>
       </c>
       <c r="AK22" s="3" t="n">
         <v>45629.625</v>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3352,25 +3352,25 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Sparta Praha</t>
+          <t>Maccabi Netanya</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Karviná</t>
+          <t>Ashdod</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I23" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
@@ -3378,83 +3378,83 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.23</v>
+        <v>1.9</v>
       </c>
       <c r="M23" t="n">
-        <v>6.3</v>
+        <v>3.4</v>
       </c>
       <c r="N23" t="n">
-        <v>10.7</v>
+        <v>3.6</v>
       </c>
       <c r="O23" t="n">
-        <v>1.5</v>
+        <v>2.6</v>
       </c>
       <c r="P23" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S23" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="V23" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="X23" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AA23" t="n">
         <v>3.1</v>
       </c>
-      <c r="Q23" t="n">
-        <v>9</v>
-      </c>
-      <c r="R23" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="S23" t="n">
-        <v>4</v>
-      </c>
-      <c r="T23" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="U23" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="V23" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W23" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="X23" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>2.17</v>
-      </c>
       <c r="AB23" t="n">
-        <v>1.65</v>
+        <v>1.34</v>
       </c>
       <c r="AC23" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AD23" t="n">
         <v>2</v>
       </c>
-      <c r="AD23" t="n">
-        <v>1.73</v>
-      </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>['2', '39', '45', '88']</t>
+          <t>['27', '44']</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>['36']</t>
+          <t>['54', '54']</t>
         </is>
       </c>
       <c r="AG23" t="n">
-        <v>1.05</v>
+        <v>1.22</v>
       </c>
       <c r="AH23" t="n">
-        <v>4.33</v>
+        <v>1.68</v>
       </c>
       <c r="AI23" t="n">
-        <v>1.17</v>
+        <v>1.57</v>
       </c>
       <c r="AJ23" t="n">
-        <v>4.7</v>
+        <v>2.6</v>
       </c>
       <c r="AK23" s="3" t="n">
         <v>45629.625</v>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3481,25 +3481,25 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Vaduz</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I24" t="n">
         <v>0</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
@@ -3507,83 +3507,83 @@
         </is>
       </c>
       <c r="L24" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="M24" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="N24" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="O24" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="P24" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="S24" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="V24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W24" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="X24" t="n">
+        <v>4.45</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AA24" t="n">
         <v>2.28</v>
       </c>
-      <c r="M24" t="n">
-        <v>3.66</v>
-      </c>
-      <c r="N24" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="O24" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="P24" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="R24" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="S24" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="T24" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="U24" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="V24" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="W24" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="X24" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>5</v>
-      </c>
       <c r="AB24" t="n">
-        <v>1.17</v>
+        <v>1.58</v>
       </c>
       <c r="AC24" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AE24" t="inlineStr">
+        <is>
+          <t>['78']</t>
+        </is>
+      </c>
+      <c r="AF24" t="inlineStr">
+        <is>
+          <t>['14']</t>
+        </is>
+      </c>
+      <c r="AG24" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AI24" t="n">
         <v>2.1</v>
       </c>
-      <c r="AD24" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AE24" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF24" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG24" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AH24" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AI24" t="n">
-        <v>2.2</v>
-      </c>
       <c r="AJ24" t="n">
-        <v>1.95</v>
+        <v>1.73</v>
       </c>
       <c r="AK24" s="3" t="n">
         <v>45629.64583333334</v>
@@ -3600,7 +3600,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3610,25 +3610,25 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vaduz</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I25" t="n">
         <v>0</v>
       </c>
       <c r="J25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K25" t="inlineStr">
         <is>
@@ -3636,83 +3636,83 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.75</v>
+        <v>2.28</v>
       </c>
       <c r="M25" t="n">
+        <v>3.66</v>
+      </c>
+      <c r="N25" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="O25" t="n">
         <v>3.6</v>
       </c>
-      <c r="N25" t="n">
+      <c r="P25" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="R25" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="S25" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="T25" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="V25" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="W25" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="X25" t="n">
         <v>2.3</v>
       </c>
-      <c r="O25" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="P25" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="R25" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="S25" t="n">
-        <v>3.54</v>
-      </c>
-      <c r="T25" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="U25" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="V25" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W25" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="X25" t="n">
-        <v>4.45</v>
-      </c>
       <c r="Y25" t="n">
-        <v>1.53</v>
+        <v>2.37</v>
       </c>
       <c r="Z25" t="n">
-        <v>2.38</v>
+        <v>1.48</v>
       </c>
       <c r="AA25" t="n">
-        <v>2.28</v>
+        <v>5</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.58</v>
+        <v>1.17</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.44</v>
+        <v>2.1</v>
       </c>
       <c r="AD25" t="n">
-        <v>2.63</v>
+        <v>1.67</v>
       </c>
       <c r="AE25" t="inlineStr">
         <is>
-          <t>['78']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF25" t="inlineStr">
         <is>
-          <t>['14']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG25" t="n">
-        <v>1.61</v>
+        <v>1.47</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="AI25" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AJ25" t="n">
-        <v>1.73</v>
+        <v>1.95</v>
       </c>
       <c r="AK25" s="3" t="n">
         <v>45629.64583333334</v>
@@ -3997,109 +3997,109 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="G28" t="n">
+        <v>2</v>
+      </c>
+      <c r="H28" t="n">
+        <v>2</v>
+      </c>
+      <c r="I28" t="n">
+        <v>2</v>
+      </c>
+      <c r="J28" t="n">
         <v>1</v>
       </c>
-      <c r="H28" t="n">
-        <v>1</v>
-      </c>
-      <c r="I28" t="n">
-        <v>0</v>
-      </c>
-      <c r="J28" t="n">
-        <v>0</v>
-      </c>
       <c r="K28" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
       <c r="L28" t="n">
-        <v>3.3</v>
+        <v>1.37</v>
       </c>
       <c r="M28" t="n">
-        <v>3.3</v>
+        <v>4.85</v>
       </c>
       <c r="N28" t="n">
-        <v>2.19</v>
+        <v>7.75</v>
       </c>
       <c r="O28" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="P28" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="R28" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S28" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="T28" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="V28" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W28" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="X28" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AE28" t="inlineStr">
+        <is>
+          <t>['12', '20']</t>
+        </is>
+      </c>
+      <c r="AF28" t="inlineStr">
+        <is>
+          <t>['26', '90+7']</t>
+        </is>
+      </c>
+      <c r="AG28" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AI28" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AJ28" t="n">
         <v>3.55</v>
-      </c>
-      <c r="P28" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="R28" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="S28" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="T28" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="U28" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="V28" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="W28" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="X28" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y28" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="Z28" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AE28" t="inlineStr">
-        <is>
-          <t>['53']</t>
-        </is>
-      </c>
-      <c r="AF28" t="inlineStr">
-        <is>
-          <t>['90+4']</t>
-        </is>
-      </c>
-      <c r="AG28" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AH28" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AI28" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AJ28" t="n">
-        <v>1.91</v>
       </c>
       <c r="AK28" s="3" t="n">
         <v>45629.69791666666</v>
@@ -4116,7 +4116,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4126,25 +4126,25 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H29" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I29" t="n">
         <v>2</v>
       </c>
       <c r="J29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K29" t="inlineStr">
         <is>
@@ -4152,83 +4152,83 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.41</v>
+        <v>3.17</v>
       </c>
       <c r="M29" t="n">
-        <v>3.54</v>
+        <v>3.5</v>
       </c>
       <c r="N29" t="n">
-        <v>2.69</v>
+        <v>2.22</v>
       </c>
       <c r="O29" t="n">
-        <v>2.95</v>
+        <v>4</v>
       </c>
       <c r="P29" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.2</v>
+        <v>2.75</v>
       </c>
       <c r="R29" t="n">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="S29" t="n">
-        <v>2.95</v>
+        <v>2.75</v>
       </c>
       <c r="T29" t="n">
-        <v>2.55</v>
+        <v>2.75</v>
       </c>
       <c r="U29" t="n">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="V29" t="n">
         <v>1.05</v>
       </c>
       <c r="W29" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="X29" t="n">
-        <v>3.95</v>
+        <v>3.55</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.68</v>
+        <v>1.88</v>
       </c>
       <c r="Z29" t="n">
-        <v>2.08</v>
+        <v>1.92</v>
       </c>
       <c r="AA29" t="n">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.42</v>
+        <v>1.35</v>
       </c>
       <c r="AC29" t="n">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="AD29" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AE29" t="inlineStr">
         <is>
-          <t>['1', '26', '82']</t>
+          <t>['2', '22']</t>
         </is>
       </c>
       <c r="AF29" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['27', '54']</t>
         </is>
       </c>
       <c r="AG29" t="n">
-        <v>1.44</v>
+        <v>1.7</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.55</v>
+        <v>1.3</v>
       </c>
       <c r="AI29" t="n">
-        <v>1.95</v>
+        <v>2.38</v>
       </c>
       <c r="AJ29" t="n">
-        <v>2.05</v>
+        <v>1.67</v>
       </c>
       <c r="AK29" s="3" t="n">
         <v>45629.69791666666</v>
@@ -4255,22 +4255,22 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Harrogate Town</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G30" t="n">
+        <v>5</v>
+      </c>
+      <c r="H30" t="n">
         <v>2</v>
       </c>
-      <c r="H30" t="n">
-        <v>0</v>
-      </c>
       <c r="I30" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -4281,22 +4281,22 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.72</v>
+        <v>2.2</v>
       </c>
       <c r="M30" t="n">
-        <v>3.75</v>
+        <v>3.46</v>
       </c>
       <c r="N30" t="n">
-        <v>4.6</v>
+        <v>3.1</v>
       </c>
       <c r="O30" t="n">
-        <v>2.3</v>
+        <v>2.85</v>
       </c>
       <c r="P30" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="Q30" t="n">
-        <v>4.75</v>
+        <v>3.55</v>
       </c>
       <c r="R30" t="n">
         <v>1.4</v>
@@ -4311,19 +4311,19 @@
         <v>1.4</v>
       </c>
       <c r="V30" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="W30" t="n">
         <v>1.3</v>
       </c>
       <c r="X30" t="n">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.95</v>
+        <v>1.92</v>
       </c>
       <c r="Z30" t="n">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="AA30" t="n">
         <v>3.35</v>
@@ -4332,32 +4332,32 @@
         <v>1.3</v>
       </c>
       <c r="AC30" t="n">
-        <v>1.83</v>
+        <v>1.7</v>
       </c>
       <c r="AD30" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE30" t="inlineStr">
+        <is>
+          <t>['2', '11', '19', '33', '68']</t>
+        </is>
+      </c>
+      <c r="AF30" t="inlineStr">
+        <is>
+          <t>['63', '80']</t>
+        </is>
+      </c>
+      <c r="AG30" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AH30" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AI30" t="n">
         <v>1.85</v>
       </c>
-      <c r="AE30" t="inlineStr">
-        <is>
-          <t>['10', '72']</t>
-        </is>
-      </c>
-      <c r="AF30" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG30" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AH30" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AI30" t="n">
-        <v>1.57</v>
-      </c>
       <c r="AJ30" t="n">
-        <v>2.8</v>
+        <v>2.25</v>
       </c>
       <c r="AK30" s="3" t="n">
         <v>45629.69791666666</v>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4384,22 +4384,22 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Connah's Quay</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Caernarfon Town</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I31" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -4410,13 +4410,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2.26</v>
+        <v>2.31</v>
       </c>
       <c r="M31" t="n">
-        <v>3.44</v>
+        <v>3.5</v>
       </c>
       <c r="N31" t="n">
-        <v>3.01</v>
+        <v>2.69</v>
       </c>
       <c r="O31" t="n">
         <v>2.88</v>
@@ -4425,68 +4425,68 @@
         <v>2.2</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.75</v>
+        <v>3.25</v>
       </c>
       <c r="R31" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S31" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="T31" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="V31" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W31" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="X31" t="n">
+        <v>3.88</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AE31" t="inlineStr">
+        <is>
+          <t>['34']</t>
+        </is>
+      </c>
+      <c r="AF31" t="inlineStr">
+        <is>
+          <t>['60']</t>
+        </is>
+      </c>
+      <c r="AG31" t="n">
         <v>1.4</v>
       </c>
-      <c r="S31" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="T31" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="U31" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V31" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="W31" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="X31" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="Y31" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="Z31" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AA31" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AB31" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AC31" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AD31" t="n">
-        <v>2</v>
-      </c>
-      <c r="AE31" t="inlineStr">
-        <is>
-          <t>['9', '12', '26', '38']</t>
-        </is>
-      </c>
-      <c r="AF31" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG31" t="n">
-        <v>1.3</v>
-      </c>
       <c r="AH31" t="n">
-        <v>1.57</v>
+        <v>1.52</v>
       </c>
       <c r="AI31" t="n">
         <v>1.73</v>
       </c>
       <c r="AJ31" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="AK31" s="3" t="n">
         <v>45629.69791666666</v>
@@ -4513,109 +4513,109 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Morecambe</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="G32" t="n">
+        <v>1</v>
+      </c>
+      <c r="H32" t="n">
+        <v>1</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0</v>
+      </c>
+      <c r="J32" t="n">
+        <v>0</v>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L32" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="M32" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="N32" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="O32" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="P32" t="n">
         <v>2</v>
       </c>
-      <c r="H32" t="n">
-        <v>2</v>
-      </c>
-      <c r="I32" t="n">
-        <v>0</v>
-      </c>
-      <c r="J32" t="n">
-        <v>1</v>
-      </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L32" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="M32" t="n">
-        <v>3.62</v>
-      </c>
-      <c r="N32" t="n">
-        <v>4.17</v>
-      </c>
-      <c r="O32" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="P32" t="n">
-        <v>2.1</v>
-      </c>
       <c r="Q32" t="n">
-        <v>4.33</v>
+        <v>4</v>
       </c>
       <c r="R32" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="S32" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="T32" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="U32" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="V32" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="W32" t="n">
         <v>1.4</v>
       </c>
-      <c r="S32" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="T32" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="U32" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="V32" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="W32" t="n">
-        <v>1.3</v>
-      </c>
       <c r="X32" t="n">
-        <v>3.4</v>
+        <v>2.9</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.96</v>
+        <v>2.16</v>
       </c>
       <c r="Z32" t="n">
-        <v>1.84</v>
+        <v>1.63</v>
       </c>
       <c r="AA32" t="n">
-        <v>3.4</v>
+        <v>4.2</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="AC32" t="n">
-        <v>1.77</v>
+        <v>1.85</v>
       </c>
       <c r="AD32" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="AE32" t="inlineStr">
         <is>
-          <t>['48', '75']</t>
+          <t>['79']</t>
         </is>
       </c>
       <c r="AF32" t="inlineStr">
         <is>
-          <t>['12', '50']</t>
+          <t>['57']</t>
         </is>
       </c>
       <c r="AG32" t="n">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="AH32" t="n">
-        <v>1.93</v>
+        <v>1.7</v>
       </c>
       <c r="AI32" t="n">
-        <v>1.65</v>
+        <v>1.8</v>
       </c>
       <c r="AJ32" t="n">
-        <v>2.65</v>
+        <v>2.45</v>
       </c>
       <c r="AK32" s="3" t="n">
         <v>45629.69791666666</v>
@@ -4632,7 +4632,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4642,22 +4642,22 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="G33" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H33" t="n">
         <v>0</v>
       </c>
       <c r="I33" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -4668,16 +4668,16 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="M33" t="n">
-        <v>3.52</v>
+        <v>3.44</v>
       </c>
       <c r="N33" t="n">
-        <v>3.11</v>
+        <v>3.01</v>
       </c>
       <c r="O33" t="n">
-        <v>2.75</v>
+        <v>2.88</v>
       </c>
       <c r="P33" t="n">
         <v>2.2</v>
@@ -4686,10 +4686,10 @@
         <v>3.75</v>
       </c>
       <c r="R33" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="S33" t="n">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="T33" t="n">
         <v>2.75</v>
@@ -4701,32 +4701,32 @@
         <v>1.05</v>
       </c>
       <c r="W33" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="X33" t="n">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.82</v>
+        <v>1.93</v>
       </c>
       <c r="Z33" t="n">
-        <v>1.98</v>
+        <v>1.87</v>
       </c>
       <c r="AA33" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="AC33" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AD33" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AE33" t="inlineStr">
         <is>
-          <t>['90+2']</t>
+          <t>['9', '12', '26', '38']</t>
         </is>
       </c>
       <c r="AF33" t="inlineStr">
@@ -4735,16 +4735,16 @@
         </is>
       </c>
       <c r="AG33" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AH33" t="n">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="AI33" t="n">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="AJ33" t="n">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="AK33" s="3" t="n">
         <v>45629.69791666666</v>
@@ -4761,7 +4761,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4771,109 +4771,109 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Briton Ferry</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Newtown</t>
         </is>
       </c>
       <c r="G34" t="n">
         <v>2</v>
       </c>
       <c r="H34" t="n">
+        <v>1</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0</v>
+      </c>
+      <c r="J34" t="n">
+        <v>0</v>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L34" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="M34" t="n">
+        <v>3.66</v>
+      </c>
+      <c r="N34" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="O34" t="n">
+        <v>3</v>
+      </c>
+      <c r="P34" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="R34" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="S34" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="T34" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="U34" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="V34" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W34" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X34" t="n">
+        <v>4.55</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AE34" t="inlineStr">
+        <is>
+          <t>['79', '90+17']</t>
+        </is>
+      </c>
+      <c r="AF34" t="inlineStr">
+        <is>
+          <t>['71']</t>
+        </is>
+      </c>
+      <c r="AG34" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AH34" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AI34" t="n">
         <v>2</v>
       </c>
-      <c r="I34" t="n">
-        <v>2</v>
-      </c>
-      <c r="J34" t="n">
-        <v>1</v>
-      </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L34" t="n">
-        <v>3.17</v>
-      </c>
-      <c r="M34" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="N34" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="O34" t="n">
-        <v>4</v>
-      </c>
-      <c r="P34" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Q34" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="R34" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S34" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="T34" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="U34" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V34" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="W34" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="X34" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="Y34" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="Z34" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AA34" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AB34" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AC34" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AD34" t="n">
-        <v>2</v>
-      </c>
-      <c r="AE34" t="inlineStr">
-        <is>
-          <t>['2', '22']</t>
-        </is>
-      </c>
-      <c r="AF34" t="inlineStr">
-        <is>
-          <t>['27', '54']</t>
-        </is>
-      </c>
-      <c r="AG34" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AH34" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AI34" t="n">
-        <v>2.38</v>
-      </c>
       <c r="AJ34" t="n">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AK34" s="3" t="n">
         <v>45629.69791666666</v>
@@ -5019,7 +5019,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5029,23 +5029,23 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="G36" t="n">
+        <v>3</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0</v>
+      </c>
+      <c r="I36" t="n">
         <v>2</v>
       </c>
-      <c r="H36" t="n">
-        <v>0</v>
-      </c>
-      <c r="I36" t="n">
-        <v>0</v>
-      </c>
       <c r="J36" t="n">
         <v>0</v>
       </c>
@@ -5055,83 +5055,83 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>1.83</v>
+        <v>2.41</v>
       </c>
       <c r="M36" t="n">
-        <v>3.45</v>
+        <v>3.54</v>
       </c>
       <c r="N36" t="n">
-        <v>4.64</v>
+        <v>2.69</v>
       </c>
       <c r="O36" t="n">
-        <v>2.5</v>
+        <v>2.95</v>
       </c>
       <c r="P36" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="R36" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="S36" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="T36" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="U36" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="V36" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W36" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X36" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AE36" t="inlineStr">
+        <is>
+          <t>['1', '26', '82']</t>
+        </is>
+      </c>
+      <c r="AF36" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG36" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AH36" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AI36" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AJ36" t="n">
         <v>2.05</v>
-      </c>
-      <c r="Q36" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="R36" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="S36" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="T36" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="U36" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="V36" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="W36" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="X36" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="Y36" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="Z36" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AA36" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="AB36" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AC36" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AD36" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AE36" t="inlineStr">
-        <is>
-          <t>['89', '90+1']</t>
-        </is>
-      </c>
-      <c r="AF36" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG36" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AH36" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AI36" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AJ36" t="n">
-        <v>3</v>
       </c>
       <c r="AK36" s="3" t="n">
         <v>45629.69791666666</v>
@@ -5158,109 +5158,109 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="G37" t="n">
+        <v>1</v>
+      </c>
+      <c r="H37" t="n">
+        <v>1</v>
+      </c>
+      <c r="I37" t="n">
+        <v>0</v>
+      </c>
+      <c r="J37" t="n">
+        <v>0</v>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L37" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="M37" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="N37" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="O37" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="P37" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="R37" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="S37" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="T37" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="U37" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="V37" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="W37" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="X37" t="n">
         <v>3</v>
       </c>
-      <c r="H37" t="n">
-        <v>2</v>
-      </c>
-      <c r="I37" t="n">
-        <v>0</v>
-      </c>
-      <c r="J37" t="n">
-        <v>0</v>
-      </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L37" t="n">
+      <c r="Y37" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AE37" t="inlineStr">
+        <is>
+          <t>['53']</t>
+        </is>
+      </c>
+      <c r="AF37" t="inlineStr">
+        <is>
+          <t>['90+4']</t>
+        </is>
+      </c>
+      <c r="AG37" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AH37" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AI37" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AJ37" t="n">
         <v>1.91</v>
-      </c>
-      <c r="M37" t="n">
-        <v>3.72</v>
-      </c>
-      <c r="N37" t="n">
-        <v>3.67</v>
-      </c>
-      <c r="O37" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="P37" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="Q37" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="R37" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S37" t="n">
-        <v>3</v>
-      </c>
-      <c r="T37" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="U37" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="V37" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="W37" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="X37" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="Y37" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="Z37" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AA37" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AB37" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AC37" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AD37" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AE37" t="inlineStr">
-        <is>
-          <t>['57', '64', '86']</t>
-        </is>
-      </c>
-      <c r="AF37" t="inlineStr">
-        <is>
-          <t>['74', '90+4']</t>
-        </is>
-      </c>
-      <c r="AG37" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AH37" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AI37" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AJ37" t="n">
-        <v>2.4</v>
       </c>
       <c r="AK37" s="3" t="n">
         <v>45629.69791666666</v>
@@ -5287,22 +5287,22 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Harrogate Town</t>
         </is>
       </c>
       <c r="G38" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H38" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I38" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -5313,22 +5313,22 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>2.2</v>
+        <v>1.72</v>
       </c>
       <c r="M38" t="n">
-        <v>3.46</v>
+        <v>3.75</v>
       </c>
       <c r="N38" t="n">
-        <v>3.1</v>
+        <v>4.6</v>
       </c>
       <c r="O38" t="n">
-        <v>2.85</v>
+        <v>2.3</v>
       </c>
       <c r="P38" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="Q38" t="n">
-        <v>3.55</v>
+        <v>4.75</v>
       </c>
       <c r="R38" t="n">
         <v>1.4</v>
@@ -5343,19 +5343,19 @@
         <v>1.4</v>
       </c>
       <c r="V38" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="W38" t="n">
         <v>1.3</v>
       </c>
       <c r="X38" t="n">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="Z38" t="n">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="AA38" t="n">
         <v>3.35</v>
@@ -5364,32 +5364,32 @@
         <v>1.3</v>
       </c>
       <c r="AC38" t="n">
-        <v>1.7</v>
+        <v>1.83</v>
       </c>
       <c r="AD38" t="n">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AE38" t="inlineStr">
         <is>
-          <t>['2', '11', '19', '33', '68']</t>
+          <t>['10', '72']</t>
         </is>
       </c>
       <c r="AF38" t="inlineStr">
         <is>
-          <t>['63', '80']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG38" t="n">
-        <v>1.35</v>
+        <v>1.18</v>
       </c>
       <c r="AH38" t="n">
-        <v>1.62</v>
+        <v>2.05</v>
       </c>
       <c r="AI38" t="n">
-        <v>1.85</v>
+        <v>1.57</v>
       </c>
       <c r="AJ38" t="n">
-        <v>2.25</v>
+        <v>2.8</v>
       </c>
       <c r="AK38" s="3" t="n">
         <v>45629.69791666666</v>
@@ -5406,7 +5406,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5416,16 +5416,16 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="G39" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H39" t="n">
         <v>2</v>
@@ -5434,7 +5434,7 @@
         <v>0</v>
       </c>
       <c r="J39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K39" t="inlineStr">
         <is>
@@ -5442,83 +5442,83 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>1.73</v>
+        <v>1.91</v>
       </c>
       <c r="M39" t="n">
-        <v>3.75</v>
+        <v>3.72</v>
       </c>
       <c r="N39" t="n">
-        <v>4.82</v>
+        <v>3.67</v>
       </c>
       <c r="O39" t="n">
-        <v>2.25</v>
+        <v>2.5</v>
       </c>
       <c r="P39" t="n">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="Q39" t="n">
-        <v>5.5</v>
+        <v>3.85</v>
       </c>
       <c r="R39" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="S39" t="n">
         <v>3</v>
       </c>
       <c r="T39" t="n">
-        <v>2.75</v>
+        <v>2.45</v>
       </c>
       <c r="U39" t="n">
-        <v>1.4</v>
+        <v>1.48</v>
       </c>
       <c r="V39" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="W39" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="X39" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AE39" t="inlineStr">
+        <is>
+          <t>['57', '64', '86']</t>
+        </is>
+      </c>
+      <c r="AF39" t="inlineStr">
+        <is>
+          <t>['74', '90+4']</t>
+        </is>
+      </c>
+      <c r="AG39" t="n">
         <v>1.28</v>
       </c>
-      <c r="X39" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="Y39" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="Z39" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AA39" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AB39" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AC39" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AD39" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AE39" t="inlineStr">
-        <is>
-          <t>['68']</t>
-        </is>
-      </c>
-      <c r="AF39" t="inlineStr">
-        <is>
-          <t>['33', '80']</t>
-        </is>
-      </c>
-      <c r="AG39" t="n">
-        <v>1.17</v>
-      </c>
       <c r="AH39" t="n">
-        <v>2.15</v>
+        <v>1.8</v>
       </c>
       <c r="AI39" t="n">
-        <v>1.44</v>
+        <v>1.7</v>
       </c>
       <c r="AJ39" t="n">
-        <v>3</v>
+        <v>2.4</v>
       </c>
       <c r="AK39" s="3" t="n">
         <v>45629.69791666666</v>
@@ -5535,7 +5535,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5545,109 +5545,109 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Connah's Quay</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Caernarfon Town</t>
+          <t>Morecambe</t>
         </is>
       </c>
       <c r="G40" t="n">
+        <v>2</v>
+      </c>
+      <c r="H40" t="n">
+        <v>2</v>
+      </c>
+      <c r="I40" t="n">
+        <v>0</v>
+      </c>
+      <c r="J40" t="n">
         <v>1</v>
       </c>
-      <c r="H40" t="n">
-        <v>1</v>
-      </c>
-      <c r="I40" t="n">
-        <v>1</v>
-      </c>
-      <c r="J40" t="n">
-        <v>0</v>
-      </c>
       <c r="K40" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
       <c r="L40" t="n">
-        <v>2.31</v>
+        <v>1.82</v>
       </c>
       <c r="M40" t="n">
-        <v>3.5</v>
+        <v>3.62</v>
       </c>
       <c r="N40" t="n">
-        <v>2.69</v>
+        <v>4.17</v>
       </c>
       <c r="O40" t="n">
-        <v>2.88</v>
+        <v>2.4</v>
       </c>
       <c r="P40" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="Q40" t="n">
-        <v>3.25</v>
+        <v>4.33</v>
       </c>
       <c r="R40" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="S40" t="n">
-        <v>3.25</v>
+        <v>2.75</v>
       </c>
       <c r="T40" t="n">
-        <v>2.63</v>
+        <v>2.8</v>
       </c>
       <c r="U40" t="n">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="V40" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="W40" t="n">
-        <v>1.16</v>
+        <v>1.3</v>
       </c>
       <c r="X40" t="n">
-        <v>3.88</v>
+        <v>3.4</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.58</v>
+        <v>1.96</v>
       </c>
       <c r="Z40" t="n">
-        <v>2.28</v>
+        <v>1.84</v>
       </c>
       <c r="AA40" t="n">
-        <v>2.61</v>
+        <v>3.4</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AC40" t="n">
-        <v>1.62</v>
+        <v>1.77</v>
       </c>
       <c r="AD40" t="n">
-        <v>2.2</v>
+        <v>1.9</v>
       </c>
       <c r="AE40" t="inlineStr">
         <is>
-          <t>['34']</t>
+          <t>['48', '75']</t>
         </is>
       </c>
       <c r="AF40" t="inlineStr">
         <is>
-          <t>['60']</t>
+          <t>['12', '50']</t>
         </is>
       </c>
       <c r="AG40" t="n">
-        <v>1.4</v>
+        <v>1.22</v>
       </c>
       <c r="AH40" t="n">
-        <v>1.52</v>
+        <v>1.93</v>
       </c>
       <c r="AI40" t="n">
-        <v>1.73</v>
+        <v>1.65</v>
       </c>
       <c r="AJ40" t="n">
-        <v>2.1</v>
+        <v>2.65</v>
       </c>
       <c r="AK40" s="3" t="n">
         <v>45629.69791666666</v>
@@ -5674,81 +5674,81 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="G41" t="n">
+        <v>1</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0</v>
+      </c>
+      <c r="I41" t="n">
+        <v>0</v>
+      </c>
+      <c r="J41" t="n">
+        <v>0</v>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L41" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="M41" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="N41" t="n">
+        <v>3.11</v>
+      </c>
+      <c r="O41" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="P41" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="R41" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S41" t="n">
         <v>3</v>
       </c>
-      <c r="H41" t="n">
-        <v>1</v>
-      </c>
-      <c r="I41" t="n">
-        <v>0</v>
-      </c>
-      <c r="J41" t="n">
-        <v>1</v>
-      </c>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L41" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="M41" t="n">
-        <v>4.15</v>
-      </c>
-      <c r="N41" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="O41" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="P41" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="Q41" t="n">
-        <v>5</v>
-      </c>
-      <c r="R41" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S41" t="n">
-        <v>3.25</v>
-      </c>
       <c r="T41" t="n">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="U41" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="V41" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="W41" t="n">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="X41" t="n">
-        <v>4</v>
+        <v>3.55</v>
       </c>
       <c r="Y41" t="n">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="Z41" t="n">
-        <v>2.08</v>
+        <v>1.98</v>
       </c>
       <c r="AA41" t="n">
-        <v>2.6</v>
+        <v>3.1</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.44</v>
+        <v>1.35</v>
       </c>
       <c r="AC41" t="n">
         <v>1.7</v>
@@ -5758,25 +5758,25 @@
       </c>
       <c r="AE41" t="inlineStr">
         <is>
-          <t>['75', '80', '85']</t>
+          <t>['90+2']</t>
         </is>
       </c>
       <c r="AF41" t="inlineStr">
         <is>
-          <t>['34']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG41" t="n">
-        <v>1.15</v>
+        <v>1.33</v>
       </c>
       <c r="AH41" t="n">
-        <v>2.25</v>
+        <v>1.67</v>
       </c>
       <c r="AI41" t="n">
-        <v>1.44</v>
+        <v>1.67</v>
       </c>
       <c r="AJ41" t="n">
-        <v>2.88</v>
+        <v>2.38</v>
       </c>
       <c r="AK41" s="3" t="n">
         <v>45629.69791666666</v>
@@ -5793,7 +5793,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5803,16 +5803,16 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Briton Ferry</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Newtown</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="G42" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H42" t="n">
         <v>1</v>
@@ -5821,7 +5821,7 @@
         <v>0</v>
       </c>
       <c r="J42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K42" t="inlineStr">
         <is>
@@ -5829,83 +5829,83 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>2.49</v>
+        <v>1.63</v>
       </c>
       <c r="M42" t="n">
-        <v>3.66</v>
+        <v>4.15</v>
       </c>
       <c r="N42" t="n">
-        <v>2.41</v>
+        <v>5.1</v>
       </c>
       <c r="O42" t="n">
-        <v>3</v>
+        <v>2.2</v>
       </c>
       <c r="P42" t="n">
         <v>2.38</v>
       </c>
       <c r="Q42" t="n">
+        <v>5</v>
+      </c>
+      <c r="R42" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S42" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="T42" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="U42" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="V42" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W42" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="X42" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AB42" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AE42" t="inlineStr">
+        <is>
+          <t>['75', '80', '85']</t>
+        </is>
+      </c>
+      <c r="AF42" t="inlineStr">
+        <is>
+          <t>['34']</t>
+        </is>
+      </c>
+      <c r="AG42" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AH42" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AI42" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AJ42" t="n">
         <v>2.88</v>
-      </c>
-      <c r="R42" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="S42" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="T42" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="U42" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="V42" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W42" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="X42" t="n">
-        <v>4.55</v>
-      </c>
-      <c r="Y42" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="Z42" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="AA42" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AB42" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AC42" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AD42" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AE42" t="inlineStr">
-        <is>
-          <t>['79', '90+17']</t>
-        </is>
-      </c>
-      <c r="AF42" t="inlineStr">
-        <is>
-          <t>['71']</t>
-        </is>
-      </c>
-      <c r="AG42" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AH42" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AI42" t="n">
-        <v>2</v>
-      </c>
-      <c r="AJ42" t="n">
-        <v>1.8</v>
       </c>
       <c r="AK42" s="3" t="n">
         <v>45629.69791666666</v>
@@ -5922,7 +5922,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5932,22 +5932,22 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="G43" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H43" t="n">
         <v>2</v>
       </c>
       <c r="I43" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J43" t="n">
         <v>1</v>
@@ -5958,83 +5958,83 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>1.37</v>
+        <v>1.73</v>
       </c>
       <c r="M43" t="n">
-        <v>4.85</v>
+        <v>3.75</v>
       </c>
       <c r="N43" t="n">
-        <v>7.75</v>
+        <v>4.82</v>
       </c>
       <c r="O43" t="n">
-        <v>1.8</v>
+        <v>2.25</v>
       </c>
       <c r="P43" t="n">
-        <v>2.45</v>
+        <v>2.25</v>
       </c>
       <c r="Q43" t="n">
-        <v>6.25</v>
+        <v>5.5</v>
       </c>
       <c r="R43" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="S43" t="n">
+        <v>3</v>
+      </c>
+      <c r="T43" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U43" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V43" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W43" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="X43" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AA43" t="n">
         <v>3.2</v>
       </c>
-      <c r="T43" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="U43" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="V43" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W43" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="X43" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="Y43" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="Z43" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AA43" t="n">
-        <v>2.7</v>
-      </c>
       <c r="AB43" t="n">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AC43" t="n">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="AD43" t="n">
-        <v>1.75</v>
+        <v>1.91</v>
       </c>
       <c r="AE43" t="inlineStr">
         <is>
-          <t>['12', '20']</t>
+          <t>['68']</t>
         </is>
       </c>
       <c r="AF43" t="inlineStr">
         <is>
-          <t>['26', '90+7']</t>
+          <t>['33', '80']</t>
         </is>
       </c>
       <c r="AG43" t="n">
-        <v>1.07</v>
+        <v>1.17</v>
       </c>
       <c r="AH43" t="n">
-        <v>3.1</v>
+        <v>2.15</v>
       </c>
       <c r="AI43" t="n">
-        <v>1.35</v>
+        <v>1.44</v>
       </c>
       <c r="AJ43" t="n">
-        <v>3.55</v>
+        <v>3</v>
       </c>
       <c r="AK43" s="3" t="n">
         <v>45629.69791666666</v>
@@ -6051,7 +6051,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -6061,19 +6061,19 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="G44" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I44" t="n">
         <v>0</v>
@@ -6087,83 +6087,83 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>1.93</v>
+        <v>1.83</v>
       </c>
       <c r="M44" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="N44" t="n">
-        <v>3.95</v>
+        <v>4.64</v>
       </c>
       <c r="O44" t="n">
-        <v>2.75</v>
+        <v>2.5</v>
       </c>
       <c r="P44" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="Q44" t="n">
-        <v>4</v>
+        <v>5.5</v>
       </c>
       <c r="R44" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="S44" t="n">
         <v>2.5</v>
       </c>
       <c r="T44" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="U44" t="n">
         <v>1.3</v>
       </c>
       <c r="V44" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="W44" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="X44" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="Y44" t="n">
-        <v>2.16</v>
+        <v>2.28</v>
       </c>
       <c r="Z44" t="n">
-        <v>1.63</v>
+        <v>1.57</v>
       </c>
       <c r="AA44" t="n">
-        <v>4.2</v>
+        <v>4.33</v>
       </c>
       <c r="AB44" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AC44" t="n">
-        <v>1.85</v>
+        <v>2.05</v>
       </c>
       <c r="AD44" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="AE44" t="inlineStr">
         <is>
-          <t>['79']</t>
+          <t>['89', '90+1']</t>
         </is>
       </c>
       <c r="AF44" t="inlineStr">
         <is>
-          <t>['57']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG44" t="n">
-        <v>1.28</v>
+        <v>1.18</v>
       </c>
       <c r="AH44" t="n">
-        <v>1.7</v>
+        <v>1.95</v>
       </c>
       <c r="AI44" t="n">
-        <v>1.8</v>
+        <v>1.53</v>
       </c>
       <c r="AJ44" t="n">
-        <v>2.45</v>
+        <v>3</v>
       </c>
       <c r="AK44" s="3" t="n">
         <v>45629.69791666666</v>
@@ -6438,7 +6438,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -6448,16 +6448,16 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="G47" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H47" t="n">
         <v>1</v>
@@ -6474,83 +6474,83 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>2.82</v>
+        <v>2.4</v>
       </c>
       <c r="M47" t="n">
-        <v>3.71</v>
+        <v>3.22</v>
       </c>
       <c r="N47" t="n">
-        <v>2.49</v>
+        <v>3.09</v>
       </c>
       <c r="O47" t="n">
         <v>3.25</v>
       </c>
       <c r="P47" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="Q47" t="n">
-        <v>3.1</v>
+        <v>3.6</v>
       </c>
       <c r="R47" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="S47" t="n">
-        <v>3.25</v>
+        <v>2.5</v>
       </c>
       <c r="T47" t="n">
-        <v>2.63</v>
+        <v>3.5</v>
       </c>
       <c r="U47" t="n">
-        <v>1.44</v>
+        <v>1.29</v>
       </c>
       <c r="V47" t="n">
-        <v>1.02</v>
+        <v>1.09</v>
       </c>
       <c r="W47" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="X47" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="Y47" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="Z47" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AA47" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AB47" t="n">
         <v>1.2</v>
       </c>
-      <c r="X47" t="n">
-        <v>3.74</v>
-      </c>
-      <c r="Y47" t="n">
+      <c r="AC47" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD47" t="n">
         <v>1.75</v>
       </c>
-      <c r="Z47" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AA47" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="AB47" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AC47" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AD47" t="n">
-        <v>2.25</v>
-      </c>
       <c r="AE47" t="inlineStr">
         <is>
-          <t>['2', '61', '90']</t>
+          <t>['21', '77']</t>
         </is>
       </c>
       <c r="AF47" t="inlineStr">
         <is>
-          <t>['90+3']</t>
+          <t>['50']</t>
         </is>
       </c>
       <c r="AG47" t="n">
-        <v>1.55</v>
+        <v>1.4</v>
       </c>
       <c r="AH47" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="AI47" t="n">
-        <v>2.05</v>
+        <v>1.83</v>
       </c>
       <c r="AJ47" t="n">
-        <v>1.83</v>
+        <v>2.2</v>
       </c>
       <c r="AK47" s="3" t="n">
         <v>45629.71875</v>
@@ -6567,7 +6567,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6577,16 +6577,16 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="G48" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H48" t="n">
         <v>1</v>
@@ -6603,83 +6603,83 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>2.4</v>
+        <v>2.82</v>
       </c>
       <c r="M48" t="n">
-        <v>3.22</v>
+        <v>3.71</v>
       </c>
       <c r="N48" t="n">
-        <v>3.09</v>
+        <v>2.49</v>
       </c>
       <c r="O48" t="n">
         <v>3.25</v>
       </c>
       <c r="P48" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="Q48" t="n">
-        <v>3.6</v>
+        <v>3.1</v>
       </c>
       <c r="R48" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="S48" t="n">
-        <v>2.5</v>
+        <v>3.25</v>
       </c>
       <c r="T48" t="n">
-        <v>3.5</v>
+        <v>2.63</v>
       </c>
       <c r="U48" t="n">
-        <v>1.29</v>
+        <v>1.44</v>
       </c>
       <c r="V48" t="n">
-        <v>1.09</v>
+        <v>1.02</v>
       </c>
       <c r="W48" t="n">
-        <v>1.42</v>
+        <v>1.2</v>
       </c>
       <c r="X48" t="n">
-        <v>2.8</v>
+        <v>3.74</v>
       </c>
       <c r="Y48" t="n">
-        <v>2.35</v>
+        <v>1.75</v>
       </c>
       <c r="Z48" t="n">
-        <v>1.54</v>
+        <v>2.05</v>
       </c>
       <c r="AA48" t="n">
-        <v>4.33</v>
+        <v>2.71</v>
       </c>
       <c r="AB48" t="n">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AC48" t="n">
-        <v>2</v>
+        <v>1.57</v>
       </c>
       <c r="AD48" t="n">
-        <v>1.75</v>
+        <v>2.25</v>
       </c>
       <c r="AE48" t="inlineStr">
         <is>
-          <t>['21', '77']</t>
+          <t>['2', '61', '90']</t>
         </is>
       </c>
       <c r="AF48" t="inlineStr">
         <is>
-          <t>['50']</t>
+          <t>['90+3']</t>
         </is>
       </c>
       <c r="AG48" t="n">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="AH48" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="AI48" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AJ48" t="n">
         <v>1.83</v>
-      </c>
-      <c r="AJ48" t="n">
-        <v>2.2</v>
       </c>
       <c r="AK48" s="3" t="n">
         <v>45629.71875</v>
